--- a/data_lake/macro/Japan/Japan CPI YoY.xlsx
+++ b/data_lake/macro/Japan/Japan CPI YoY.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\Japan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14973709-F02D-4C85-B79E-0BD0189D3CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F939BA-3F0E-4297-A3FF-E3975AA5B746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A0358DA5-9C11-4628-B2D7-24F5FD1145D7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A0358DA5-9C11-4628-B2D7-24F5FD1145D7}"/>
   </bookViews>
   <sheets>
-    <sheet name="JPCPI YoY" sheetId="1" r:id="rId1"/>
+    <sheet name="JPCPIYOY" sheetId="1" r:id="rId1"/>
     <sheet name="JCPNEFEY" sheetId="3" r:id="rId2"/>
     <sheet name="info" sheetId="2" r:id="rId3"/>
   </sheets>
@@ -92,7 +92,7 @@
     <numFmt numFmtId="177" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="179" formatCode="0.0%"/>
-    <numFmt numFmtId="185" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="180" formatCode="yyyy/mm/dd;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -224,7 +224,7 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
